--- a/administrative_forms/033_team_coach_time_off_form--administrative_forms.xlsx
+++ b/administrative_forms/033_team_coach_time_off_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{0:_'select_one',_1:_'personal',_2:_'family',_3:_'vacation'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{0: 'Select One', 1: 'Personal', 2: 'Family', 3: 'Vacation'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'start_date',_'label':_'start_date',_'hint':_none,_'type':_'date',_'options':_[]}</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'start_date', 'label': 'Start Date', 'hint': None, 'type': 'date', 'options': []}</t>
+          <t>Start Date</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'end_date',_'label':_'end_date',_'hint':_none,_'type':_'date',_'options':_[]}</t>
+          <t>end_date</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'end_date', 'label': 'End Date', 'hint': None, 'type': 'date', 'options': []}</t>
+          <t>End Date</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'coach_name',_'label':_'coach_name',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>coach_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'coach_name', 'label': 'Coach Name', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>Coach Name</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'team',_'label':_'team',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'team', 'label': 'Team', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'coach_position',_'label':_'coach_position',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>coach_position</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'coach_position', 'label': 'Coach Position', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>Coach Position</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'notes',_'label':_'notes',_'hint':_none,_'type':_'note',_'options':_[]}</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'notes', 'label': 'Notes', 'hint': None, 'type': 'note', 'options': []}</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'submit',_'label':_'submit',_'hint':_none,_'type':_'select_multiple',_'options':_[]}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'submit', 'label': 'Submit', 'hint': None, 'type': 'select_multiple', 'options': []}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'confirm',_'label':_'confirm',_'hint':_none,_'type':_'boolean',_'options':_[]}</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'confirm', 'label': 'Confirm', 'hint': None, 'type': 'boolean', 'options': []}</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
